--- a/excel/metricas-diarias/04_Metricas_Diarias_Embudo_Webinar_Pago.xlsx
+++ b/excel/metricas-diarias/04_Metricas_Diarias_Embudo_Webinar_Pago.xlsx
@@ -1239,21 +1239,11 @@
       <c r="J6" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="K6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="13" t="n"/>
       <c r="P6" s="14">
         <f>IF(COUNT(C6:O6)=0,"",IFERROR(C6/D6*1000,0))</f>
         <v/>
@@ -1373,44 +1363,34 @@
         <v/>
       </c>
       <c r="C7" s="9" t="n">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>79265</v>
+        <v>83639</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>51246</v>
+        <v>52096</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>1697</v>
+        <v>1510</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1348</v>
+        <v>1266</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>6</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="n"/>
       <c r="P7" s="14">
         <f>IF(COUNT(C7:O7)=0,"",IFERROR(C7/D7*1000,0))</f>
         <v/>
@@ -1530,44 +1510,34 @@
         <v/>
       </c>
       <c r="C8" s="9" t="n">
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>72187</v>
+        <v>101109</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>45990</v>
+        <v>60415</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1285</v>
+        <v>2248</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1262</v>
+        <v>2051</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="13" t="n"/>
       <c r="P8" s="14">
         <f>IF(COUNT(C8:O8)=0,"",IFERROR(C8/D8*1000,0))</f>
         <v/>
@@ -1687,40 +1657,40 @@
         <v/>
       </c>
       <c r="C9" s="9" t="n">
-        <v>446</v>
+        <v>380</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>86770</v>
+        <v>75476</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>63028</v>
+        <v>56265</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1533</v>
+        <v>1397</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1359</v>
+        <v>1153</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="N9" s="13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O9" s="13" t="n">
         <v>1</v>
@@ -1844,38 +1814,38 @@
         <v/>
       </c>
       <c r="C10" s="9" t="n">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>90929</v>
+        <v>83581</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>61148</v>
+        <v>55723</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1793</v>
+        <v>1737</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1707</v>
+        <v>1513</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>2</v>
       </c>
       <c r="N10" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="13" t="n">
         <v>0</v>
@@ -1999,44 +1969,34 @@
         <v/>
       </c>
       <c r="C11" s="9" t="n">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>88900</v>
+        <v>88967</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>57043</v>
+        <v>56494</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1760</v>
+        <v>1700</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1466</v>
+        <v>1399</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="n"/>
       <c r="P11" s="14">
         <f>IF(COUNT(C11:O11)=0,"",IFERROR(C11/D11*1000,0))</f>
         <v/>
@@ -2156,44 +2116,34 @@
         <v/>
       </c>
       <c r="C12" s="9" t="n">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>88967</v>
+        <v>93737</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>56494</v>
+        <v>57692</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1700</v>
+        <v>1824</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1399</v>
+        <v>1781</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
       <c r="P12" s="14">
         <f>IF(COUNT(C12:O12)=0,"",IFERROR(C12/D12*1000,0))</f>
         <v/>
@@ -2313,44 +2263,34 @@
         <v/>
       </c>
       <c r="C13" s="9" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>72496</v>
+        <v>72837</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>49514</v>
+        <v>48910</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>1571</v>
+        <v>1625</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1344</v>
+        <v>1395</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
       <c r="P13" s="14">
         <f>IF(COUNT(C13:O13)=0,"",IFERROR(C13/D13*1000,0))</f>
         <v/>
@@ -2470,44 +2410,34 @@
         <v/>
       </c>
       <c r="C14" s="9" t="n">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>105858</v>
+        <v>97114</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>75856</v>
+        <v>71864</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>2326</v>
+        <v>1864</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>2032</v>
+        <v>1823</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>48</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
       <c r="P14" s="14">
         <f>IF(COUNT(C14:O14)=0,"",IFERROR(C14/D14*1000,0))</f>
         <v/>
@@ -2627,44 +2557,34 @@
         <v/>
       </c>
       <c r="C15" s="9" t="n">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>93460</v>
+        <v>89317</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>60429</v>
+        <v>66577</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>1994</v>
+        <v>1914</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1658</v>
+        <v>1554</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
       <c r="P15" s="14">
         <f>IF(COUNT(C15:O15)=0,"",IFERROR(C15/D15*1000,0))</f>
         <v/>
@@ -2784,40 +2704,40 @@
         <v/>
       </c>
       <c r="C16" s="9" t="n">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>74272</v>
+        <v>75418</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46627</v>
+        <v>55165</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>1349</v>
+        <v>1560</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1115</v>
+        <v>1247</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>109</v>
+      </c>
+      <c r="L16" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="K16" s="13" t="n">
-        <v>66</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>13</v>
-      </c>
       <c r="M16" s="13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O16" s="13" t="n">
         <v>1</v>
@@ -2944,16 +2864,16 @@
         <v>461</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>99855</v>
+        <v>96813</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>65636</v>
+        <v>59085</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>1972</v>
+        <v>1802</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1606</v>
+        <v>1545</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>42</v>
@@ -2966,13 +2886,13 @@
       </c>
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="13" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>2</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" s="13" t="n">
         <v>0</v>
@@ -3096,19 +3016,19 @@
         <v/>
       </c>
       <c r="C18" s="9" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>75770</v>
+        <v>69580</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>55634</v>
+        <v>49815</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>1487</v>
+        <v>1311</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="H18" s="13" t="n">
         <v>29</v>
@@ -3117,23 +3037,13 @@
         <v>6</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
       <c r="P18" s="14">
         <f>IF(COUNT(C18:O18)=0,"",IFERROR(C18/D18*1000,0))</f>
         <v/>
@@ -3253,44 +3163,34 @@
         <v/>
       </c>
       <c r="C19" s="9" t="n">
-        <v>479</v>
+        <v>386</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>89223</v>
+        <v>85617</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>62416</v>
+        <v>55967</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1949</v>
+        <v>1607</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1596</v>
+        <v>1448</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
       <c r="P19" s="14">
         <f>IF(COUNT(C19:O19)=0,"",IFERROR(C19/D19*1000,0))</f>
         <v/>
@@ -3410,19 +3310,19 @@
         <v/>
       </c>
       <c r="C20" s="9" t="n">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>90242</v>
+        <v>95851</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>66545</v>
+        <v>62777</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>2017</v>
+        <v>2086</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1653</v>
+        <v>1696</v>
       </c>
       <c r="H20" s="13" t="n">
         <v>39</v>
@@ -3433,21 +3333,11 @@
       <c r="J20" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="K20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="13" t="n"/>
       <c r="P20" s="14">
         <f>IF(COUNT(C20:O20)=0,"",IFERROR(C20/D20*1000,0))</f>
         <v/>
@@ -3567,44 +3457,34 @@
         <v/>
       </c>
       <c r="C21" s="9" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>95551</v>
+        <v>98480</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>66974</v>
+        <v>70934</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>1715</v>
+        <v>2083</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1361</v>
+        <v>2027</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
       <c r="P21" s="14">
         <f>IF(COUNT(C21:O21)=0,"",IFERROR(C21/D21*1000,0))</f>
         <v/>
@@ -3724,44 +3604,34 @@
         <v/>
       </c>
       <c r="C22" s="9" t="n">
-        <v>403</v>
+        <v>469</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>78781</v>
+        <v>91612</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>54189</v>
+        <v>62248</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>1558</v>
+        <v>1658</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>1522</v>
+        <v>1298</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="K22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
       <c r="P22" s="14">
         <f>IF(COUNT(C22:O22)=0,"",IFERROR(C22/D22*1000,0))</f>
         <v/>
@@ -3881,19 +3751,19 @@
         <v/>
       </c>
       <c r="C23" s="9" t="n">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>80461</v>
+        <v>95811</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>58060</v>
+        <v>59269</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>1476</v>
+        <v>1961</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1426</v>
+        <v>1640</v>
       </c>
       <c r="H23" s="13" t="n">
         <v>38</v>
@@ -3902,19 +3772,19 @@
         <v>8</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O23" s="13" t="n">
         <v>1</v>
@@ -4038,38 +3908,38 @@
         <v/>
       </c>
       <c r="C24" s="9" t="n">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>75272</v>
+        <v>80423</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>45384</v>
+        <v>52184</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>1396</v>
+        <v>1524</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>1361</v>
+        <v>1475</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I24" s="13" t="n">
         <v>7</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K24" s="13" t="n"/>
       <c r="L24" s="13" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>2</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="13" t="n">
         <v>0</v>
@@ -4193,44 +4063,34 @@
         <v/>
       </c>
       <c r="C25" s="9" t="n">
-        <v>441</v>
+        <v>406</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>89830</v>
+        <v>82309</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>66179</v>
+        <v>61344</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>1598</v>
+        <v>1518</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1562</v>
+        <v>1294</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>7</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="K25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="13" t="n"/>
+      <c r="O25" s="13" t="n"/>
       <c r="P25" s="14">
         <f>IF(COUNT(C25:O25)=0,"",IFERROR(C25/D25*1000,0))</f>
         <v/>
@@ -4350,44 +4210,34 @@
         <v/>
       </c>
       <c r="C26" s="9" t="n">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>95811</v>
+        <v>76022</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>59269</v>
+        <v>45441</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>1961</v>
+        <v>1578</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>1640</v>
+        <v>1452</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="K26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
       <c r="P26" s="14">
         <f>IF(COUNT(C26:O26)=0,"",IFERROR(C26/D26*1000,0))</f>
         <v/>
@@ -4507,44 +4357,34 @@
         <v/>
       </c>
       <c r="C27" s="9" t="n">
-        <v>453</v>
+        <v>382</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>101001</v>
+        <v>86401</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>72029</v>
+        <v>52438</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>2049</v>
+        <v>1811</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>1955</v>
+        <v>1771</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="K27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="n"/>
       <c r="P27" s="14">
         <f>IF(COUNT(C27:O27)=0,"",IFERROR(C27/D27*1000,0))</f>
         <v/>
@@ -4664,44 +4504,34 @@
         <v/>
       </c>
       <c r="C28" s="9" t="n">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>74047</v>
+        <v>81144</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>53140</v>
+        <v>56554</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>1309</v>
+        <v>1817</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1088</v>
+        <v>1436</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="K28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
       <c r="P28" s="14">
         <f>IF(COUNT(C28:O28)=0,"",IFERROR(C28/D28*1000,0))</f>
         <v/>
@@ -4821,44 +4651,34 @@
         <v/>
       </c>
       <c r="C29" s="9" t="n">
-        <v>385</v>
+        <v>471</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>83409</v>
+        <v>89185</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>57414</v>
+        <v>56686</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1697</v>
+        <v>1909</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>1361</v>
+        <v>1847</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="n"/>
       <c r="P29" s="14">
         <f>IF(COUNT(C29:O29)=0,"",IFERROR(C29/D29*1000,0))</f>
         <v/>
@@ -4978,40 +4798,40 @@
         <v/>
       </c>
       <c r="C30" s="9" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>84343</v>
+        <v>86564</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>54188</v>
+        <v>58880</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>1764</v>
+        <v>1852</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>1584</v>
+        <v>1772</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M30" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="N30" s="13" t="n">
         <v>10</v>
-      </c>
-      <c r="N30" s="13" t="n">
-        <v>4</v>
       </c>
       <c r="O30" s="13" t="n">
         <v>1</v>
@@ -5135,38 +4955,38 @@
         <v/>
       </c>
       <c r="C31" s="9" t="n">
-        <v>380</v>
+        <v>441</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>69233</v>
+        <v>98134</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>44032</v>
+        <v>63305</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>1538</v>
+        <v>2195</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>1198</v>
+        <v>2108</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="K31" s="13" t="n"/>
       <c r="L31" s="13" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="M31" s="13" t="n">
         <v>2</v>
       </c>
       <c r="N31" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="13" t="n">
         <v>0</v>
@@ -5290,44 +5110,34 @@
         <v/>
       </c>
       <c r="C32" s="9" t="n">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>81144</v>
+        <v>89120</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>56554</v>
+        <v>60274</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>1817</v>
+        <v>1927</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1436</v>
+        <v>1526</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="K32" s="13" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="n"/>
       <c r="P32" s="14">
         <f>IF(COUNT(C32:O32)=0,"",IFERROR(C32/D32*1000,0))</f>
         <v/>
@@ -5447,44 +5257,34 @@
         <v/>
       </c>
       <c r="C33" s="9" t="n">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>82927</v>
+        <v>88495</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>52308</v>
+        <v>63081</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>1740</v>
+        <v>1854</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="13" t="n"/>
+      <c r="N33" s="13" t="n"/>
+      <c r="O33" s="13" t="n"/>
       <c r="P33" s="14">
         <f>IF(COUNT(C33:O33)=0,"",IFERROR(C33/D33*1000,0))</f>
         <v/>
